--- a/exports/trend_1d/PHOENIXLTD_full_report.xlsx
+++ b/exports/trend_1d/PHOENIXLTD_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q51"/>
+  <dimension ref="A1:U51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>9.84</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42045</v>
+        <v>42046</v>
       </c>
       <c r="H2" t="n">
-        <v>189.7</v>
+        <v>185.9</v>
       </c>
       <c r="I2" t="n">
         <v>186.0277183715256</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K2" t="n">
-        <v>3.89</v>
+        <v>1.81</v>
       </c>
       <c r="L2" t="n">
         <v>3.5</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>9.369999999999999</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42174</v>
+        <v>42177</v>
       </c>
       <c r="H3" t="n">
-        <v>188.35</v>
+        <v>191.1</v>
       </c>
       <c r="I3" t="n">
         <v>189.8285332291192</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.32</v>
+        <v>-2.8</v>
       </c>
       <c r="L3" t="n">
         <v>8.93</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>5</v>
+      </c>
+      <c r="U3" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>9.92</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42235</v>
+        <v>42236</v>
       </c>
       <c r="H4" t="n">
-        <v>178.9</v>
+        <v>174.4</v>
       </c>
       <c r="I4" t="n">
         <v>175.6718672274526</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K4" t="n">
-        <v>-6.38</v>
+        <v>-8.74</v>
       </c>
       <c r="L4" t="n">
         <v>10.13</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>9.369999999999999</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42325</v>
+        <v>42326</v>
       </c>
       <c r="H5" t="n">
-        <v>169.45</v>
+        <v>178.4</v>
       </c>
       <c r="I5" t="n">
         <v>175.4899828120768</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K5" t="n">
-        <v>2.84</v>
+        <v>-2.29</v>
       </c>
       <c r="L5" t="n">
-        <v>2.64</v>
+        <v>2.92</v>
       </c>
       <c r="M5" t="n">
         <v>5.99</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>11.61</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42345</v>
+        <v>42346</v>
       </c>
       <c r="H6" t="n">
-        <v>168.85</v>
+        <v>162.9</v>
       </c>
       <c r="I6" t="n">
         <v>164.9433947614504</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K6" t="n">
-        <v>-5.35</v>
+        <v>-8.69</v>
       </c>
       <c r="L6" t="n">
-        <v>6.11</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="M6" t="n">
         <v>2.94</v>
       </c>
       <c r="N6" t="n">
-        <v>2.26</v>
+        <v>3.52</v>
       </c>
       <c r="O6" t="n">
         <v>5.28</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>11.79</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42437</v>
+        <v>42438</v>
       </c>
       <c r="H7" t="n">
-        <v>143.7</v>
+        <v>153.1</v>
       </c>
       <c r="I7" t="n">
         <v>147.173250099404</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K7" t="n">
-        <v>11.79</v>
+        <v>6.02</v>
       </c>
       <c r="L7" t="n">
         <v>7.43</v>
@@ -840,7 +923,7 @@
         <v>3.95</v>
       </c>
       <c r="N7" t="n">
-        <v>5.51</v>
+        <v>6.54</v>
       </c>
       <c r="O7" t="n">
         <v>-3.52</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>18.07</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42641</v>
+        <v>42642</v>
       </c>
       <c r="H8" t="n">
-        <v>198.2</v>
+        <v>185.9</v>
       </c>
       <c r="I8" t="n">
         <v>192.9084671625046</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K8" t="n">
-        <v>29.46</v>
+        <v>21.42</v>
       </c>
       <c r="L8" t="n">
         <v>7.09</v>
@@ -897,7 +992,7 @@
         <v>4.57</v>
       </c>
       <c r="N8" t="n">
-        <v>5.29</v>
+        <v>6.21</v>
       </c>
       <c r="O8" t="n">
         <v>6.54</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>137</v>
+        <v>138</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>7</v>
+      </c>
+      <c r="U8" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -933,28 +1040,28 @@
         <v>16.25</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42699</v>
+        <v>42702</v>
       </c>
       <c r="H9" t="n">
-        <v>175.8</v>
+        <v>199.5</v>
       </c>
       <c r="I9" t="n">
         <v>191.2531813167551</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K9" t="n">
-        <v>5.43</v>
+        <v>-7.32</v>
       </c>
       <c r="L9" t="n">
-        <v>7.58</v>
+        <v>13.47</v>
       </c>
       <c r="M9" t="n">
         <v>7.16</v>
       </c>
       <c r="N9" t="n">
-        <v>9.19</v>
+        <v>13.48</v>
       </c>
       <c r="O9" t="n">
         <v>-6.21</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>24.63</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>43000</v>
+        <v>43003</v>
       </c>
       <c r="H10" t="n">
-        <v>244.2</v>
+        <v>236.1</v>
       </c>
       <c r="I10" t="n">
         <v>237.092755115922</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="K10" t="n">
-        <v>22.41</v>
+        <v>18.35</v>
       </c>
       <c r="L10" t="n">
         <v>14.51</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>206</v>
+        <v>207</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>10</v>
+      </c>
+      <c r="U10" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>10.14</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>43012</v>
+        <v>43013</v>
       </c>
       <c r="H11" t="n">
-        <v>255.05</v>
+        <v>275</v>
       </c>
       <c r="I11" t="n">
         <v>260.0389935475538</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K11" t="n">
-        <v>-8.029999999999999</v>
+        <v>-16.48</v>
       </c>
       <c r="L11" t="n">
-        <v>9.640000000000001</v>
+        <v>19.23</v>
       </c>
       <c r="M11" t="n">
         <v>1.42</v>
       </c>
       <c r="N11" t="n">
-        <v>3.39</v>
+        <v>7.82</v>
       </c>
       <c r="O11" t="n">
         <v>-3.32</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>13.45</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>43060</v>
+        <v>43061</v>
       </c>
       <c r="H12" t="n">
-        <v>252</v>
+        <v>242.45</v>
       </c>
       <c r="I12" t="n">
         <v>247.1357062566731</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K12" t="n">
-        <v>-8.359999999999999</v>
+        <v>-11.84</v>
       </c>
       <c r="L12" t="n">
-        <v>8.91</v>
+        <v>12.85</v>
       </c>
       <c r="M12" t="n">
         <v>1.97</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>14.81</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>43075</v>
+        <v>43076</v>
       </c>
       <c r="H13" t="n">
-        <v>275.7</v>
+        <v>279.85</v>
       </c>
       <c r="I13" t="n">
         <v>278.3655960344506</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K13" t="n">
-        <v>-13.71</v>
+        <v>-15.43</v>
       </c>
       <c r="L13" t="n">
         <v>20.64</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>11.43</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>43152</v>
+        <v>43153</v>
       </c>
       <c r="H14" t="n">
-        <v>292.5</v>
+        <v>283.1</v>
       </c>
       <c r="I14" t="n">
         <v>292.3644337033621</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K14" t="n">
-        <v>4.52</v>
+        <v>1.16</v>
       </c>
       <c r="L14" t="n">
         <v>1.55</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>15.44</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>43160</v>
+        <v>43164</v>
       </c>
       <c r="H15" t="n">
-        <v>303</v>
+        <v>325.55</v>
       </c>
       <c r="I15" t="n">
         <v>323.5067259866586</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K15" t="n">
-        <v>-7.03</v>
+        <v>-14.99</v>
       </c>
       <c r="L15" t="n">
-        <v>12.36</v>
+        <v>16.92</v>
       </c>
       <c r="M15" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>5.1</v>
+        <v>7.44</v>
       </c>
       <c r="O15" t="n">
         <v>-3.21</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>43187</v>
+      </c>
+      <c r="S15" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>18.02</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43199</v>
+        <v>43200</v>
       </c>
       <c r="H16" t="n">
-        <v>290.8</v>
+        <v>287.4</v>
       </c>
       <c r="I16" t="n">
         <v>288.1600008902597</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K16" t="n">
-        <v>-10.67</v>
+        <v>-11.72</v>
       </c>
       <c r="L16" t="n">
-        <v>11.75</v>
+        <v>12.3</v>
       </c>
       <c r="M16" t="n">
         <v>3.65</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43187</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>12.79</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43231</v>
+        <v>43234</v>
       </c>
       <c r="H17" t="n">
-        <v>309.55</v>
+        <v>325.4</v>
       </c>
       <c r="I17" t="n">
         <v>318.0705488706189</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K17" t="n">
-        <v>-7.71</v>
+        <v>-13.22</v>
       </c>
       <c r="L17" t="n">
-        <v>13.67</v>
+        <v>14.82</v>
       </c>
       <c r="M17" t="n">
         <v>5.17</v>
       </c>
       <c r="N17" t="n">
-        <v>3.79</v>
+        <v>5.12</v>
       </c>
       <c r="O17" t="n">
         <v>-1.17</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>12.54</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43258</v>
+        <v>43259</v>
       </c>
       <c r="H18" t="n">
-        <v>323.6</v>
+        <v>320.1</v>
       </c>
       <c r="I18" t="n">
         <v>321.5917978330188</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.55</v>
+        <v>-1.63</v>
       </c>
       <c r="L18" t="n">
         <v>4.7</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,25 +1730,25 @@
         <v>12.51</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43409</v>
+        <v>43410</v>
       </c>
       <c r="H19" t="n">
-        <v>291.7</v>
+        <v>300.75</v>
       </c>
       <c r="I19" t="n">
         <v>299.8389787587511</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K19" t="n">
-        <v>8.869999999999999</v>
+        <v>6.04</v>
       </c>
       <c r="L19" t="n">
         <v>6.87</v>
       </c>
       <c r="M19" t="n">
-        <v>2.48</v>
+        <v>3.53</v>
       </c>
       <c r="N19" t="n">
         <v>5.07</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>101</v>
+        <v>102</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>6</v>
+      </c>
+      <c r="U19" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>11.58</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43461</v>
+        <v>43462</v>
       </c>
       <c r="H20" t="n">
-        <v>283.6</v>
+        <v>278.25</v>
       </c>
       <c r="I20" t="n">
         <v>280.5882690196522</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K20" t="n">
-        <v>-5.7</v>
+        <v>-7.48</v>
       </c>
       <c r="L20" t="n">
-        <v>8.16</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M20" t="n">
         <v>1.57</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>11.6</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43487</v>
+        <v>43488</v>
       </c>
       <c r="H21" t="n">
-        <v>299.5</v>
+        <v>301.9</v>
       </c>
       <c r="I21" t="n">
         <v>300.7650123964455</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K21" t="n">
-        <v>-7.64</v>
+        <v>-8.5</v>
       </c>
       <c r="L21" t="n">
-        <v>8.16</v>
+        <v>9.07</v>
       </c>
       <c r="M21" t="n">
         <v>0.99</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>9.050000000000001</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43573</v>
+        <v>43577</v>
       </c>
       <c r="H22" t="n">
-        <v>306.5</v>
+        <v>303.2</v>
       </c>
       <c r="I22" t="n">
         <v>303.4717377037314</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="K22" t="n">
-        <v>1.52</v>
+        <v>0.43</v>
       </c>
       <c r="L22" t="n">
         <v>7.93</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>4</v>
+      </c>
+      <c r="U22" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>12.54</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43615</v>
+        <v>43616</v>
       </c>
       <c r="H23" t="n">
-        <v>314.65</v>
+        <v>325.7</v>
       </c>
       <c r="I23" t="n">
         <v>321.852137688957</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.78</v>
+        <v>-7.42</v>
       </c>
       <c r="L23" t="n">
-        <v>6.86</v>
+        <v>8.01</v>
       </c>
       <c r="M23" t="n">
         <v>2.39</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43580</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>12.89</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43889</v>
+        <v>43892</v>
       </c>
       <c r="H24" t="n">
-        <v>428.2</v>
+        <v>404.4</v>
       </c>
       <c r="I24" t="n">
         <v>405.3974754112178</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="K24" t="n">
-        <v>31.47</v>
+        <v>24.16</v>
       </c>
       <c r="L24" t="n">
         <v>7.89</v>
@@ -1809,7 +2096,7 @@
         <v>2.1</v>
       </c>
       <c r="N24" t="n">
-        <v>5.1</v>
+        <v>5.56</v>
       </c>
       <c r="O24" t="n">
         <v>3.51</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>186</v>
+        <v>187</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43643</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>10</v>
+      </c>
+      <c r="U24" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>17.59</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43983</v>
+        <v>43984</v>
       </c>
       <c r="H25" t="n">
-        <v>284.2</v>
+        <v>297.2</v>
       </c>
       <c r="I25" t="n">
         <v>284.8786667811706</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K25" t="n">
-        <v>29.72</v>
+        <v>26.51</v>
       </c>
       <c r="L25" t="n">
         <v>9.77</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>4</v>
+      </c>
+      <c r="U25" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>20.9</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>44083</v>
+        <v>44084</v>
       </c>
       <c r="H26" t="n">
-        <v>311.5</v>
+        <v>307.25</v>
       </c>
       <c r="I26" t="n">
         <v>310.6672947169932</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K26" t="n">
-        <v>4.81</v>
+        <v>3.38</v>
       </c>
       <c r="L26" t="n">
         <v>8.26</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>4</v>
+      </c>
+      <c r="U26" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>13.05</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>44147</v>
+        <v>44148</v>
       </c>
       <c r="H27" t="n">
-        <v>301.5</v>
+        <v>311</v>
       </c>
       <c r="I27" t="n">
         <v>306.1646250030167</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K27" t="n">
-        <v>1.87</v>
+        <v>-1.22</v>
       </c>
       <c r="L27" t="n">
         <v>6.04</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2016,25 +2351,25 @@
         <v>12.95</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>44287</v>
+        <v>44291</v>
       </c>
       <c r="H28" t="n">
-        <v>383.9</v>
+        <v>366.35</v>
       </c>
       <c r="I28" t="n">
         <v>370.3583380992605</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="K28" t="n">
-        <v>23.44</v>
+        <v>17.8</v>
       </c>
       <c r="L28" t="n">
         <v>4.37</v>
       </c>
       <c r="M28" t="n">
-        <v>1.76</v>
+        <v>2.01</v>
       </c>
       <c r="N28" t="n">
         <v>7.04</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>95</v>
+        <v>96</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>6</v>
+      </c>
+      <c r="U28" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>16.28</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>44341</v>
+        <v>44342</v>
       </c>
       <c r="H29" t="n">
-        <v>385.5</v>
+        <v>402.5</v>
       </c>
       <c r="I29" t="n">
         <v>391.569788367723</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K29" t="n">
-        <v>-5.23</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="L29" t="n">
-        <v>11.16</v>
+        <v>11.23</v>
       </c>
       <c r="M29" t="n">
         <v>3.59</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>15.31</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>44428</v>
+        <v>44431</v>
       </c>
       <c r="H30" t="n">
-        <v>404.6</v>
+        <v>401.75</v>
       </c>
       <c r="I30" t="n">
         <v>402.5562182216008</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="K30" t="n">
-        <v>0.52</v>
+        <v>-0.19</v>
       </c>
       <c r="L30" t="n">
         <v>6.01</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>4</v>
+      </c>
+      <c r="U30" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>13.3</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>44461</v>
+        <v>44462</v>
       </c>
       <c r="H31" t="n">
-        <v>454.6</v>
+        <v>461.85</v>
       </c>
       <c r="I31" t="n">
         <v>455.1995250737782</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K31" t="n">
-        <v>-13.15</v>
+        <v>-14.96</v>
       </c>
       <c r="L31" t="n">
-        <v>15.18</v>
+        <v>19.35</v>
       </c>
       <c r="M31" t="n">
         <v>1.6</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>10.46</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44526</v>
+        <v>44529</v>
       </c>
       <c r="H32" t="n">
-        <v>484.2</v>
+        <v>468</v>
       </c>
       <c r="I32" t="n">
         <v>472.8066644951812</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="K32" t="n">
-        <v>4.84</v>
+        <v>1.33</v>
       </c>
       <c r="L32" t="n">
         <v>3.65</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>4</v>
+      </c>
+      <c r="U32" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>21.69</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44637</v>
+        <v>44641</v>
       </c>
       <c r="H33" t="n">
-        <v>504</v>
+        <v>517</v>
       </c>
       <c r="I33" t="n">
         <v>511.3694994716573</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="K33" t="n">
-        <v>-7.69</v>
+        <v>-10.47</v>
       </c>
       <c r="L33" t="n">
         <v>17.25</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>4</v>
+      </c>
+      <c r="U33" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>13.73</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44916</v>
+        <v>44917</v>
       </c>
       <c r="H34" t="n">
-        <v>691.9</v>
+        <v>677.3</v>
       </c>
       <c r="I34" t="n">
         <v>677.6362619893824</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K34" t="n">
-        <v>33.83</v>
+        <v>31.01</v>
       </c>
       <c r="L34" t="n">
         <v>7.6</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>189</v>
+        <v>190</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>10</v>
+      </c>
+      <c r="U34" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>11.9</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45035</v>
+        <v>45036</v>
       </c>
       <c r="H35" t="n">
-        <v>680.75</v>
+        <v>690.65</v>
       </c>
       <c r="I35" t="n">
         <v>687.7171034661563</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.51</v>
+        <v>-1.97</v>
       </c>
       <c r="L35" t="n">
         <v>7.63</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>5</v>
+      </c>
+      <c r="U35" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>10.79</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45224</v>
+        <v>45225</v>
       </c>
       <c r="H36" t="n">
-        <v>896.9</v>
+        <v>873.3</v>
       </c>
       <c r="I36" t="n">
         <v>873.924631496143</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K36" t="n">
-        <v>29.86</v>
+        <v>26.45</v>
       </c>
       <c r="L36" t="n">
         <v>3.42</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>129</v>
+        <v>130</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>7</v>
+      </c>
+      <c r="U36" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>13.06</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45231</v>
+        <v>45232</v>
       </c>
       <c r="H37" t="n">
-        <v>947.4</v>
+        <v>988.8</v>
       </c>
       <c r="I37" t="n">
         <v>987.3208816312945</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K37" t="n">
-        <v>-8.49</v>
+        <v>-13.23</v>
       </c>
       <c r="L37" t="n">
-        <v>9.07</v>
+        <v>13.94</v>
       </c>
       <c r="M37" t="n">
         <v>0.53</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>14.75</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45496</v>
+        <v>45497</v>
       </c>
       <c r="H38" t="n">
-        <v>1890.75</v>
+        <v>1782.65</v>
       </c>
       <c r="I38" t="n">
         <v>1802.296039671003</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K38" t="n">
-        <v>91.22</v>
+        <v>80.28</v>
       </c>
       <c r="L38" t="n">
         <v>5.41</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>179</v>
+        <v>180</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>9</v>
+      </c>
+      <c r="U38" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>18.72</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45618</v>
+        <v>45621</v>
       </c>
       <c r="H39" t="n">
-        <v>1627.35</v>
+        <v>1670.75</v>
       </c>
       <c r="I39" t="n">
         <v>1633.711203819806</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="K39" t="n">
-        <v>8.710000000000001</v>
+        <v>6.28</v>
       </c>
       <c r="L39" t="n">
         <v>10.4</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>5</v>
+      </c>
+      <c r="U39" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>13.8</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45645</v>
+        <v>45646</v>
       </c>
       <c r="H40" t="n">
-        <v>1672.9</v>
+        <v>1591.05</v>
       </c>
       <c r="I40" t="n">
         <v>1655.404805772568</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K40" t="n">
-        <v>0.13</v>
+        <v>-4.77</v>
       </c>
       <c r="L40" t="n">
-        <v>2.17</v>
+        <v>5.7</v>
       </c>
       <c r="M40" t="n">
         <v>1.45</v>
       </c>
       <c r="N40" t="n">
-        <v>3.82</v>
+        <v>4.89</v>
       </c>
       <c r="O40" t="n">
         <v>2.67</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>16.99</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45688</v>
+        <v>45689</v>
       </c>
       <c r="H41" t="n">
-        <v>1641.8</v>
+        <v>1764.4</v>
       </c>
       <c r="I41" t="n">
         <v>1729.858382268856</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K41" t="n">
-        <v>-3.19</v>
+        <v>-10.9</v>
       </c>
       <c r="L41" t="n">
         <v>13</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,22 +3317,22 @@
         <v>18.46</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45713</v>
+        <v>45715</v>
       </c>
       <c r="H42" t="n">
-        <v>1562.45</v>
+        <v>1511.85</v>
       </c>
       <c r="I42" t="n">
         <v>1530.877697534291</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K42" t="n">
-        <v>-11.45</v>
+        <v>-14.31</v>
       </c>
       <c r="L42" t="n">
-        <v>14.84</v>
+        <v>15.29</v>
       </c>
       <c r="M42" t="n">
         <v>2.36</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>14.83</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45888</v>
+        <v>45889</v>
       </c>
       <c r="H43" t="n">
-        <v>1503.3</v>
+        <v>1563.5</v>
       </c>
       <c r="I43" t="n">
         <v>1545.522323390468</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K43" t="n">
-        <v>0.57</v>
+        <v>-3.42</v>
       </c>
       <c r="L43" t="n">
         <v>14.82</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>117</v>
+        <v>118</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>6</v>
+      </c>
+      <c r="U43" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>9.890000000000001</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>46041</v>
+        <v>46042</v>
       </c>
       <c r="H44" t="n">
-        <v>1841</v>
+        <v>1782.8</v>
       </c>
       <c r="I44" t="n">
         <v>1836.904472394978</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K44" t="n">
-        <v>17.75</v>
+        <v>14.03</v>
       </c>
       <c r="L44" t="n">
         <v>5.93</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>103</v>
+        <v>104</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>6</v>
+      </c>
+      <c r="U44" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>10.42</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="H45" t="n">
-        <v>1758.7</v>
+        <v>1784</v>
       </c>
       <c r="I45" t="n">
         <v>1783.171989196997</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K45" t="n">
-        <v>1.35</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="L45" t="n">
         <v>3.93</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,22 +3593,22 @@
         <v>9.56</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="H46" t="n">
-        <v>1648.6</v>
+        <v>1611</v>
       </c>
       <c r="I46" t="n">
         <v>1629.508000601219</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K46" t="n">
-        <v>-7.59</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="L46" t="n">
-        <v>10.31</v>
+        <v>10.99</v>
       </c>
       <c r="M46" t="n">
         <v>3.53</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>9.75</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="H47" t="n">
-        <v>1597</v>
+        <v>1713.1</v>
       </c>
       <c r="I47" t="n">
         <v>1655.077251738325</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K47" t="n">
-        <v>0.87</v>
+        <v>-6.34</v>
       </c>
       <c r="L47" t="n">
-        <v>2.73</v>
+        <v>7.71</v>
       </c>
       <c r="M47" t="n">
-        <v>1.76</v>
+        <v>4.4</v>
       </c>
       <c r="N47" t="n">
-        <v>4.56</v>
+        <v>7.27</v>
       </c>
       <c r="O47" t="n">
         <v>-2.28</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>13.17</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="H48" t="n">
-        <v>2023.2</v>
+        <v>1910.5</v>
       </c>
       <c r="I48" t="n">
         <v>1957.583724008522</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K48" t="n">
-        <v>18.1</v>
+        <v>11.52</v>
       </c>
       <c r="L48" t="n">
         <v>3.68</v>
@@ -3177,7 +3752,7 @@
         <v>1.9</v>
       </c>
       <c r="N48" t="n">
-        <v>4.41</v>
+        <v>5.57</v>
       </c>
       <c r="O48" t="n">
         <v>7.27</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>5</v>
+      </c>
+      <c r="U48" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>11.14</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="H49" t="n">
-        <v>1953.4</v>
+        <v>1993.2</v>
       </c>
       <c r="I49" t="n">
         <v>1978.064356965162</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K49" t="n">
-        <v>-2.25</v>
+        <v>-4.33</v>
       </c>
       <c r="L49" t="n">
-        <v>4.52</v>
+        <v>5.49</v>
       </c>
       <c r="M49" t="n">
         <v>1.33</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>7.46</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="H50" t="n">
-        <v>1845.5</v>
+        <v>1771.2</v>
       </c>
       <c r="I50" t="n">
         <v>1844.514247355642</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K50" t="n">
-        <v>-7.41</v>
+        <v>-11.14</v>
       </c>
       <c r="L50" t="n">
-        <v>7.44</v>
+        <v>11.14</v>
       </c>
       <c r="M50" t="n">
         <v>1.19</v>
       </c>
       <c r="N50" t="n">
-        <v>2.66</v>
+        <v>4.03</v>
       </c>
       <c r="O50" t="n">
         <v>2.04</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3351,6 +3962,14 @@
       <c r="Q51" t="n">
         <v>14</v>
       </c>
+      <c r="R51" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8309,7 +8928,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>85.8</v>
+        <v>87.40000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -8319,7 +8938,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7">
@@ -8329,7 +8948,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="8">
@@ -8339,7 +8958,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -8349,7 +8968,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10">
@@ -8359,7 +8978,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="11">
@@ -8369,7 +8988,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
@@ -8379,7 +8998,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13">
@@ -8389,7 +9008,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>28.6</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="14">
@@ -8399,7 +9018,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.83</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="15">
@@ -8409,7 +9028,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10.17</v>
+        <v>6.52</v>
       </c>
     </row>
     <row r="16">
@@ -8419,7 +9038,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.74</v>
+        <v>-5.02</v>
       </c>
     </row>
     <row r="17">
@@ -8429,7 +9048,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>91.22</v>
+        <v>80.28</v>
       </c>
     </row>
     <row r="18">
@@ -8439,7 +9058,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>53.1</v>
+        <v>36.7</v>
       </c>
     </row>
     <row r="19">
@@ -8449,7 +9068,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8.279999999999999</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -8459,7 +9078,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7.63</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -8479,7 +9098,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23">
@@ -8489,7 +9108,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24">
@@ -8499,7 +9118,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.81</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="25">
@@ -8519,7 +9138,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.55</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27">
@@ -8539,7 +9158,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="29">
